--- a/data/trans_dic/P1001-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,99</t>
+          <t>3,02; 5,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,73</t>
+          <t>5,0; 8,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,93</t>
+          <t>4,09; 7,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,68</t>
+          <t>3,97; 7,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,51</t>
+          <t>4,78; 8,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 18,13</t>
+          <t>12,57; 18,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 15,27</t>
+          <t>10,37; 15,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 12,45</t>
+          <t>9,06; 12,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,73</t>
+          <t>4,31; 6,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 12,77</t>
+          <t>9,4; 13,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,81</t>
+          <t>7,78; 10,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 9,48</t>
+          <t>6,94; 9,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,65</t>
+          <t>4,66; 8,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,26</t>
+          <t>6,41; 10,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,41</t>
+          <t>3,75; 6,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,83</t>
+          <t>1,95; 5,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,51</t>
+          <t>5,9; 9,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,1</t>
+          <t>13,63; 18,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,09; 14,41</t>
+          <t>9,93; 14,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 13,11</t>
+          <t>9,52; 12,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,09</t>
+          <t>5,63; 8,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 13,51</t>
+          <t>10,44; 13,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,92</t>
+          <t>7,42; 9,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,6</t>
+          <t>5,13; 8,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 9,53</t>
+          <t>5,58; 9,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,64</t>
+          <t>3,76; 7,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,05</t>
+          <t>4,39; 8,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,28</t>
+          <t>6,51; 11,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,15</t>
+          <t>10,81; 16,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 15,89</t>
+          <t>10,76; 15,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,69; 15,67</t>
+          <t>10,58; 15,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 12,46</t>
+          <t>4,02; 12,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 12,02</t>
+          <t>8,74; 12,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 10,93</t>
+          <t>7,82; 11,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 11,17</t>
+          <t>8,11; 11,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,75</t>
+          <t>5,76; 10,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,19</t>
+          <t>4,99; 8,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,5</t>
+          <t>5,86; 9,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,26</t>
+          <t>6,04; 9,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,56</t>
+          <t>4,43; 7,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,15</t>
+          <t>8,5; 12,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,99; 16,68</t>
+          <t>12,35; 16,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 13,85</t>
+          <t>9,48; 13,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,17</t>
+          <t>9,63; 14,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,87</t>
+          <t>7,49; 10,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 12,42</t>
+          <t>9,75; 12,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 10,9</t>
+          <t>8,23; 10,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 10,74</t>
+          <t>7,86; 10,68</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,87</t>
+          <t>5,25; 6,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,09</t>
+          <t>6,18; 8,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,96</t>
+          <t>5,3; 6,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,68</t>
+          <t>4,36; 6,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,5</t>
+          <t>8,45; 10,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,51; 15,92</t>
+          <t>13,52; 15,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 13,29</t>
+          <t>11,03; 13,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 11,93</t>
+          <t>8,83; 12,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,42</t>
+          <t>7,14; 8,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,17; 11,69</t>
+          <t>10,18; 11,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 9,89</t>
+          <t>8,58; 9,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,2</t>
+          <t>7,22; 9,17</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20110; 41551</t>
+          <t>20934; 41387</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34773; 61404</t>
+          <t>35172; 62971</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28292; 53533</t>
+          <t>27601; 53008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25512; 48803</t>
+          <t>25223; 47261</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34923; 58567</t>
+          <t>32898; 59614</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88029; 126387</t>
+          <t>87613; 126997</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68074; 102756</t>
+          <t>69801; 104882</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60697; 84037</t>
+          <t>61149; 84833</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61313; 92981</t>
+          <t>59648; 93502</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129902; 178832</t>
+          <t>131661; 182336</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103067; 145630</t>
+          <t>104836; 145970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91287; 124234</t>
+          <t>90919; 123266</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43551; 73608</t>
+          <t>44794; 77662</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67735; 104291</t>
+          <t>65228; 102225</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37874; 65533</t>
+          <t>38342; 66273</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24814; 69585</t>
+          <t>23267; 69567</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58185; 92075</t>
+          <t>57107; 91995</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>138876; 186800</t>
+          <t>140642; 188674</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>105211; 150267</t>
+          <t>103609; 150808</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91891; 125514</t>
+          <t>91170; 124205</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>112359; 156199</t>
+          <t>108636; 155197</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>217363; 276909</t>
+          <t>213839; 277072</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>150153; 204954</t>
+          <t>153276; 206071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>102443; 184979</t>
+          <t>110231; 187596</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36985; 64653</t>
+          <t>37882; 65304</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29114; 57897</t>
+          <t>28476; 57698</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32865; 61114</t>
+          <t>33347; 62376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44402; 79493</t>
+          <t>45870; 82571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74372; 110432</t>
+          <t>73948; 109851</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83652; 123361</t>
+          <t>83496; 124041</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83882; 122990</t>
+          <t>83080; 123675</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44342; 116286</t>
+          <t>37498; 114702</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119107; 163740</t>
+          <t>119015; 164223</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119163; 167690</t>
+          <t>119903; 169374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124163; 172588</t>
+          <t>125298; 172204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97018; 176142</t>
+          <t>94343; 175610</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47153; 77211</t>
+          <t>46980; 76144</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54718; 89940</t>
+          <t>55469; 87299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55378; 86859</t>
+          <t>56606; 88795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39393; 69973</t>
+          <t>41034; 70827</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88189; 126241</t>
+          <t>88290; 128241</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>126020; 175276</t>
+          <t>129745; 176765</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97924; 144557</t>
+          <t>98989; 142255</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>107220; 155004</t>
+          <t>105297; 156024</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142930; 195577</t>
+          <t>148349; 198406</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>190828; 248058</t>
+          <t>194870; 252414</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162535; 215872</t>
+          <t>162994; 214921</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>158767; 216926</t>
+          <t>158660; 215668</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>172453; 225005</t>
+          <t>171962; 228714</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>213601; 277081</t>
+          <t>211723; 274717</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181184; 236112</t>
+          <t>179888; 236610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153091; 230943</t>
+          <t>150804; 230107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>283244; 354868</t>
+          <t>285475; 353205</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>480563; 566098</t>
+          <t>480889; 568669</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>393719; 471155</t>
+          <t>390919; 475836</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>325389; 436584</t>
+          <t>323034; 440327</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>472859; 560462</t>
+          <t>475327; 557935</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>709853; 815980</t>
+          <t>710869; 817586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>592027; 686199</t>
+          <t>595029; 687165</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>516011; 654703</t>
+          <t>514146; 652784</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1001-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,96</t>
+          <t>3,01; 5,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,95</t>
+          <t>4,96; 9,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,86</t>
+          <t>4,2; 7,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,44</t>
+          <t>4,0; 7,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,66</t>
+          <t>4,91; 8,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,22</t>
+          <t>12,23; 17,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 15,59</t>
+          <t>10,27; 15,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,57</t>
+          <t>8,94; 12,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,76</t>
+          <t>4,4; 6,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,02</t>
+          <t>9,36; 12,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,83</t>
+          <t>7,69; 10,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,41</t>
+          <t>7,08; 9,56</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,07</t>
+          <t>4,55; 7,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,05</t>
+          <t>6,43; 10,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,48</t>
+          <t>3,62; 6,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,83</t>
+          <t>4,14; 6,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,5</t>
+          <t>5,9; 9,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,28</t>
+          <t>13,51; 18,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 14,46</t>
+          <t>9,87; 14,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 12,97</t>
+          <t>9,43; 12,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,04</t>
+          <t>5,61; 7,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,44; 13,52</t>
+          <t>10,47; 13,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,98</t>
+          <t>7,36; 9,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,72</t>
+          <t>7,12; 9,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,62</t>
+          <t>5,51; 9,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,62</t>
+          <t>3,91; 7,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,21</t>
+          <t>4,31; 8,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,72</t>
+          <t>6,25; 10,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,81; 16,06</t>
+          <t>10,98; 15,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,76; 15,98</t>
+          <t>10,72; 15,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,58; 15,75</t>
+          <t>10,72; 15,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,29</t>
+          <t>10,15; 14,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 12,05</t>
+          <t>8,8; 12,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,04</t>
+          <t>7,87; 11,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,15</t>
+          <t>7,96; 11,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,72</t>
+          <t>8,64; 11,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,08</t>
+          <t>4,87; 8,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,22</t>
+          <t>5,75; 9,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,47</t>
+          <t>5,91; 9,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,65</t>
+          <t>4,2; 7,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,35</t>
+          <t>8,71; 12,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 16,82</t>
+          <t>12,28; 16,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,63</t>
+          <t>9,31; 13,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,26</t>
+          <t>11,26; 14,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,02</t>
+          <t>7,27; 9,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 12,63</t>
+          <t>9,66; 12,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 10,85</t>
+          <t>8,28; 11,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 10,68</t>
+          <t>8,23; 10,5</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,98</t>
+          <t>5,25; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,02</t>
+          <t>6,28; 8,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,97</t>
+          <t>5,26; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,65</t>
+          <t>5,25; 6,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,45</t>
+          <t>8,41; 10,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,52; 15,99</t>
+          <t>13,61; 15,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 13,42</t>
+          <t>10,96; 13,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,03</t>
+          <t>10,84; 12,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,38</t>
+          <t>7,11; 8,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 11,71</t>
+          <t>10,2; 11,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,58; 9,9</t>
+          <t>8,5; 9,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,17</t>
+          <t>8,34; 9,62</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>71888</t>
+          <t>78760</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>106778</t>
+          <t>116888</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20934; 41387</t>
+          <t>20877; 41275</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35172; 62971</t>
+          <t>34914; 63630</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27601; 53008</t>
+          <t>28331; 53457</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25223; 47261</t>
+          <t>27655; 51914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32898; 59614</t>
+          <t>33811; 59265</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87613; 126997</t>
+          <t>85265; 123556</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69801; 104882</t>
+          <t>69096; 104098</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61149; 84833</t>
+          <t>65450; 92837</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59648; 93502</t>
+          <t>60776; 94576</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131661; 182336</t>
+          <t>131057; 177986</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104836; 145970</t>
+          <t>103611; 146455</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90919; 123266</t>
+          <t>100753; 136124</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>106745</t>
+          <t>118878</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>156053</t>
+          <t>174202</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44794; 77662</t>
+          <t>43800; 74486</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65228; 102225</t>
+          <t>65381; 103338</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38342; 66273</t>
+          <t>37013; 65298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23267; 69567</t>
+          <t>43373; 70645</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57107; 91995</t>
+          <t>57110; 91856</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>140642; 188674</t>
+          <t>139459; 190334</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>103609; 150808</t>
+          <t>102949; 147211</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91170; 124205</t>
+          <t>100925; 138859</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108636; 155197</t>
+          <t>108361; 152441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>213839; 277072</t>
+          <t>214469; 274659</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153276; 206071</t>
+          <t>151910; 206334</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>110231; 187596</t>
+          <t>150825; 199201</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>64801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83664</t>
+          <t>97504</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>144459</t>
+          <t>162305</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37882; 65304</t>
+          <t>37374; 65348</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28476; 57698</t>
+          <t>29589; 56425</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33347; 62376</t>
+          <t>32751; 61873</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45870; 82571</t>
+          <t>50152; 86995</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73948; 109851</t>
+          <t>75113; 108753</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83496; 124041</t>
+          <t>83184; 122216</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83080; 123675</t>
+          <t>84190; 122658</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37498; 114702</t>
+          <t>82472; 117701</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119015; 164223</t>
+          <t>119901; 165087</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119903; 169374</t>
+          <t>120773; 169090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>125298; 172204</t>
+          <t>122878; 170601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94343; 175610</t>
+          <t>139559; 190461</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53997</t>
+          <t>54856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>132704</t>
+          <t>142868</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>186701</t>
+          <t>197723</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46980; 76144</t>
+          <t>45840; 77316</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55469; 87299</t>
+          <t>54451; 87922</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56606; 88795</t>
+          <t>55371; 89044</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41034; 70827</t>
+          <t>41511; 72015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88290; 128241</t>
+          <t>90482; 129171</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>129745; 176765</t>
+          <t>129064; 175231</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>98989; 142255</t>
+          <t>97209; 142554</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>105297; 156024</t>
+          <t>125925; 165100</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>148349; 198406</t>
+          <t>143978; 195226</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>194870; 252414</t>
+          <t>193000; 252066</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162994; 214921</t>
+          <t>164050; 217878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>158660; 215668</t>
+          <t>173312; 221134</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>213109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>593991</t>
+          <t>651118</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>171962; 228714</t>
+          <t>171921; 227118</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>211723; 274717</t>
+          <t>214993; 280066</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>179888; 236610</t>
+          <t>178431; 235824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150804; 230107</t>
+          <t>185392; 243544</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>285475; 353205</t>
+          <t>284255; 353412</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>480889; 568669</t>
+          <t>483844; 565020</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>390919; 475836</t>
+          <t>388455; 477619</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>323034; 440327</t>
+          <t>404522; 472033</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>475327; 557935</t>
+          <t>473518; 564186</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>710869; 817586</t>
+          <t>711750; 820954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>595029; 687165</t>
+          <t>589503; 686955</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>514146; 652784</t>
+          <t>605652; 698833</t>
         </is>
       </c>
     </row>
